--- a/题库/PY选择题练习.xlsx
+++ b/题库/PY选择题练习.xlsx
@@ -220,7 +220,12 @@
     <t>嵌套函数是在函数内部定义函数</t>
   </si>
   <si>
-    <t>def f(): print("Outer function f") def g(): print("Inner function g") g() f.g()</t>
+    <t>def f(): 
+  print("Outer function f") 
+def g(): 
+  print("Inner function g") 
+g() 
+f.g()</t>
   </si>
   <si>
     <t>def f(): print("Outer function f") def g(): print("Inner function") g() f()</t>
@@ -593,6 +598,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11.5"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>对下列语句不符合语法要求的表达式是</t>
     </r>
     <r>
@@ -667,6 +678,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11.5"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>已知</t>
     </r>
     <r>
@@ -726,6 +743,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11.5"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>下面代码的输出结果是</t>
     </r>
     <r>
@@ -874,7 +897,36 @@
     <t>'c'</t>
   </si>
   <si>
-    <t>下列程序的输出结果是()。try: x=1/2 except ZeroDivisionError: print('AAA')</t>
+    <r>
+      <t>下列程序的输出结果是</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11.5"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="Segoe UI"/>
+        <charset val="134"/>
+      </rPr>
+      <t>()</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11.5"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11.5"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="Segoe UI"/>
+        <charset val="134"/>
+      </rPr>
+      <t>try: x=1/2 except ZeroDivisionError: print('AAA')</t>
+    </r>
   </si>
   <si>
     <t>AAA</t>
@@ -1034,6 +1086,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11.5"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>下面代码的输出结果是</t>
     </r>
     <r>
@@ -2885,7 +2943,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" ht="187" spans="1:9">
+    <row r="13" ht="238" spans="1:9">
       <c r="A13" s="4">
         <v>12</v>
       </c>
@@ -4226,7 +4284,7 @@
       <c r="B59" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C59" s="4" t="s">
+      <c r="C59" s="6" t="s">
         <v>248</v>
       </c>
       <c r="D59" s="4">
